--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130137508</v>
+        <v>130137042</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>92092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,48 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540250</v>
+        <v>540241</v>
       </c>
       <c r="R4" t="n">
-        <v>6704316</v>
+        <v>6704273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På liten yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130137042</v>
+        <v>130137508</v>
       </c>
       <c r="B5" t="n">
-        <v>92092</v>
+        <v>98831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +1017,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540241</v>
+        <v>540250</v>
       </c>
       <c r="R5" t="n">
-        <v>6704273</v>
+        <v>6704316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På liten yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2524,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130135988</v>
+        <v>130136026</v>
       </c>
       <c r="B18" t="n">
-        <v>91937</v>
+        <v>91639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,43 +2535,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540151</v>
+        <v>540175</v>
       </c>
       <c r="R18" t="n">
-        <v>6704400</v>
+        <v>6704392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,10 +2631,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130136026</v>
+        <v>130135988</v>
       </c>
       <c r="B19" t="n">
-        <v>91639</v>
+        <v>91937</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,34 +2642,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540175</v>
+        <v>540151</v>
       </c>
       <c r="R19" t="n">
-        <v>6704392</v>
+        <v>6704400</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130135997</v>
       </c>
       <c r="B2" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130137046</v>
       </c>
       <c r="B3" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130137042</v>
       </c>
       <c r="B4" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130137508</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>130136051</v>
       </c>
       <c r="B6" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>130135971</v>
       </c>
       <c r="B7" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>130136068</v>
       </c>
       <c r="B8" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,54 +1472,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130138039</v>
+        <v>130136490</v>
       </c>
       <c r="B9" t="n">
-        <v>91937</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långslotten, Långslotten, Dlr</t>
+          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540219</v>
+        <v>540142</v>
       </c>
       <c r="R9" t="n">
-        <v>6704351</v>
+        <v>6704304</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,12 +1566,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
+          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,59 +1598,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130136490</v>
+        <v>130138039</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>91939</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
+          <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540142</v>
+        <v>540219</v>
       </c>
       <c r="R10" t="n">
-        <v>6704304</v>
+        <v>6704351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
+          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
         <v>130138048</v>
       </c>
       <c r="B11" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>130137037</v>
       </c>
       <c r="B12" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>130135979</v>
       </c>
       <c r="B13" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>130137961</v>
       </c>
       <c r="B14" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>130136085</v>
       </c>
       <c r="B15" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130136105</v>
       </c>
       <c r="B16" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130135908</v>
       </c>
       <c r="B17" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130136026</v>
+        <v>130135988</v>
       </c>
       <c r="B18" t="n">
-        <v>91639</v>
+        <v>91939</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,34 +2535,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540175</v>
+        <v>540151</v>
       </c>
       <c r="R18" t="n">
-        <v>6704392</v>
+        <v>6704400</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,10 +2640,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130135988</v>
+        <v>130136026</v>
       </c>
       <c r="B19" t="n">
-        <v>91937</v>
+        <v>91641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,43 +2651,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540151</v>
+        <v>540175</v>
       </c>
       <c r="R19" t="n">
-        <v>6704400</v>
+        <v>6704392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130135997</v>
       </c>
       <c r="B2" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130137046</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130137042</v>
+        <v>130137508</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +910,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540241</v>
+        <v>540250</v>
       </c>
       <c r="R4" t="n">
-        <v>6704273</v>
+        <v>6704316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På liten yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130137508</v>
+        <v>130137042</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,48 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540250</v>
+        <v>540241</v>
       </c>
       <c r="R5" t="n">
-        <v>6704316</v>
+        <v>6704273</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På liten yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1135,7 @@
         <v>130136051</v>
       </c>
       <c r="B6" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>130135971</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>130136068</v>
       </c>
       <c r="B8" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,59 +1472,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130136490</v>
+        <v>130138039</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>92026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
+          <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540142</v>
+        <v>540219</v>
       </c>
       <c r="R9" t="n">
-        <v>6704304</v>
+        <v>6704351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,12 +1561,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
+          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,54 +1593,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130138039</v>
+        <v>130136490</v>
       </c>
       <c r="B10" t="n">
-        <v>91939</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långslotten, Långslotten, Dlr</t>
+          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540219</v>
+        <v>540142</v>
       </c>
       <c r="R10" t="n">
-        <v>6704351</v>
+        <v>6704304</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
+          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
         <v>130138048</v>
       </c>
       <c r="B11" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>130137037</v>
       </c>
       <c r="B12" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>130135979</v>
       </c>
       <c r="B13" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>130137961</v>
       </c>
       <c r="B14" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>130136085</v>
       </c>
       <c r="B15" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130136105</v>
       </c>
       <c r="B16" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130135908</v>
       </c>
       <c r="B17" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>130135988</v>
       </c>
       <c r="B18" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>130136026</v>
       </c>
       <c r="B19" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130137508</v>
+        <v>130137042</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,48 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540250</v>
+        <v>540241</v>
       </c>
       <c r="R4" t="n">
-        <v>6704316</v>
+        <v>6704273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På liten yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130137042</v>
+        <v>130137508</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +1017,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540241</v>
+        <v>540250</v>
       </c>
       <c r="R5" t="n">
-        <v>6704273</v>
+        <v>6704316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På liten yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1472,54 +1472,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130138039</v>
+        <v>130136490</v>
       </c>
       <c r="B9" t="n">
-        <v>92026</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långslotten, Långslotten, Dlr</t>
+          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540219</v>
+        <v>540142</v>
       </c>
       <c r="R9" t="n">
-        <v>6704351</v>
+        <v>6704304</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,12 +1566,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
+          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,59 +1598,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130136490</v>
+        <v>130138039</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>92026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
+          <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540142</v>
+        <v>540219</v>
       </c>
       <c r="R10" t="n">
-        <v>6704304</v>
+        <v>6704351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
+          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -1472,59 +1472,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130136490</v>
+        <v>130138039</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>92026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
+          <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540142</v>
+        <v>540219</v>
       </c>
       <c r="R9" t="n">
-        <v>6704304</v>
+        <v>6704351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,12 +1561,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
+          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,54 +1593,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130138039</v>
+        <v>130136490</v>
       </c>
       <c r="B10" t="n">
-        <v>92026</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långslotten, Långslotten, Dlr</t>
+          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540219</v>
+        <v>540142</v>
       </c>
       <c r="R10" t="n">
-        <v>6704351</v>
+        <v>6704304</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
+          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130137037</v>
+        <v>130137961</v>
       </c>
       <c r="B12" t="n">
-        <v>92026</v>
+        <v>91728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,43 +1837,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540244</v>
+        <v>540219</v>
       </c>
       <c r="R12" t="n">
-        <v>6704273</v>
+        <v>6704341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,7 +1933,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130135979</v>
+        <v>130137037</v>
       </c>
       <c r="B13" t="n">
         <v>92026</v>
@@ -1972,7 +1963,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1982,14 +1973,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
+          <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540153</v>
+        <v>540244</v>
       </c>
       <c r="R13" t="n">
-        <v>6704402</v>
+        <v>6704273</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,12 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På samma låga som ullticka. På nytt hygge 2025. Fruktkroppar ännu små.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130137961</v>
+        <v>130135979</v>
       </c>
       <c r="B14" t="n">
-        <v>91728</v>
+        <v>92026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,34 +2060,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långslotten, Långslotten, Dlr</t>
+          <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540219</v>
+        <v>540153</v>
       </c>
       <c r="R14" t="n">
-        <v>6704341</v>
+        <v>6704402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På samma låga som ullticka. På nytt hygge 2025. Fruktkroppar ännu små.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2524,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130135988</v>
+        <v>130136026</v>
       </c>
       <c r="B18" t="n">
-        <v>92026</v>
+        <v>91728</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,43 +2535,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540151</v>
+        <v>540175</v>
       </c>
       <c r="R18" t="n">
-        <v>6704400</v>
+        <v>6704392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,10 +2631,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130136026</v>
+        <v>130135988</v>
       </c>
       <c r="B19" t="n">
-        <v>91728</v>
+        <v>92026</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,34 +2642,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540175</v>
+        <v>540151</v>
       </c>
       <c r="R19" t="n">
-        <v>6704392</v>
+        <v>6704400</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130135997</v>
       </c>
       <c r="B2" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130137046</v>
       </c>
       <c r="B3" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130137042</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>130137508</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>130136051</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>130135971</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>130136068</v>
       </c>
       <c r="B8" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,59 +1472,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130136490</v>
+        <v>130138039</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>92029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
+          <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540142</v>
+        <v>540219</v>
       </c>
       <c r="R9" t="n">
-        <v>6704304</v>
+        <v>6704351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1551,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,12 +1561,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
+          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,54 +1593,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130138039</v>
+        <v>130136490</v>
       </c>
       <c r="B10" t="n">
-        <v>92026</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långslotten, Långslotten, Dlr</t>
+          <t>Hällsjöbäcken, Hällsjöbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540219</v>
+        <v>540142</v>
       </c>
       <c r="R10" t="n">
-        <v>6704351</v>
+        <v>6704304</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Slutade räkna vid 100 på lågan... Samma låga har också ullticka och rynkskinn.</t>
+          <t>Fåtal plantor som försöker klara sig på hygget. Just på platsen lite fler sparade träd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,7 +1722,7 @@
         <v>130138048</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>130137037</v>
       </c>
       <c r="B12" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>130135979</v>
       </c>
       <c r="B13" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>130137961</v>
       </c>
       <c r="B14" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>130136085</v>
       </c>
       <c r="B15" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130136105</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130135908</v>
       </c>
       <c r="B17" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130135988</v>
+        <v>130136026</v>
       </c>
       <c r="B18" t="n">
-        <v>92026</v>
+        <v>91731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,43 +2535,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540151</v>
+        <v>540175</v>
       </c>
       <c r="R18" t="n">
-        <v>6704400</v>
+        <v>6704392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,10 +2631,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130136026</v>
+        <v>130135988</v>
       </c>
       <c r="B19" t="n">
-        <v>91728</v>
+        <v>92029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,34 +2642,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540175</v>
+        <v>540151</v>
       </c>
       <c r="R19" t="n">
-        <v>6704392</v>
+        <v>6704400</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130135997</v>
       </c>
       <c r="B2" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130137046</v>
       </c>
       <c r="B3" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130137042</v>
+        <v>130137508</v>
       </c>
       <c r="B4" t="n">
-        <v>92184</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +910,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540241</v>
+        <v>540250</v>
       </c>
       <c r="R4" t="n">
-        <v>6704273</v>
+        <v>6704316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På liten yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130137508</v>
+        <v>130137042</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,48 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540250</v>
+        <v>540241</v>
       </c>
       <c r="R5" t="n">
-        <v>6704316</v>
+        <v>6704273</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På liten yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1135,7 @@
         <v>130136051</v>
       </c>
       <c r="B6" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>130135971</v>
       </c>
       <c r="B7" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>130136068</v>
       </c>
       <c r="B8" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>130138039</v>
       </c>
       <c r="B9" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>130136490</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>130138048</v>
       </c>
       <c r="B11" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>130137037</v>
       </c>
       <c r="B12" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>130135979</v>
       </c>
       <c r="B13" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>130137961</v>
       </c>
       <c r="B14" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>130136085</v>
       </c>
       <c r="B15" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130136105</v>
       </c>
       <c r="B16" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130135908</v>
       </c>
       <c r="B17" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130136026</v>
+        <v>130135988</v>
       </c>
       <c r="B18" t="n">
-        <v>91731</v>
+        <v>92055</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,34 +2535,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540175</v>
+        <v>540151</v>
       </c>
       <c r="R18" t="n">
-        <v>6704392</v>
+        <v>6704400</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,10 +2640,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130135988</v>
+        <v>130136026</v>
       </c>
       <c r="B19" t="n">
-        <v>92029</v>
+        <v>91757</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,43 +2651,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540151</v>
+        <v>540175</v>
       </c>
       <c r="R19" t="n">
-        <v>6704400</v>
+        <v>6704392</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130135997</v>
       </c>
       <c r="B2" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130137046</v>
       </c>
       <c r="B3" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130137508</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>130137042</v>
       </c>
       <c r="B5" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>130136051</v>
       </c>
       <c r="B6" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>130135971</v>
       </c>
       <c r="B7" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>130136068</v>
       </c>
       <c r="B8" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>130138039</v>
       </c>
       <c r="B9" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>130136490</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>130138048</v>
       </c>
       <c r="B11" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130137037</v>
+        <v>130137961</v>
       </c>
       <c r="B12" t="n">
-        <v>92055</v>
+        <v>91758</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,43 +1837,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540244</v>
+        <v>540219</v>
       </c>
       <c r="R12" t="n">
-        <v>6704273</v>
+        <v>6704341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130135979</v>
+        <v>130137037</v>
       </c>
       <c r="B13" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1963,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1982,14 +1973,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
+          <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540153</v>
+        <v>540244</v>
       </c>
       <c r="R13" t="n">
-        <v>6704402</v>
+        <v>6704273</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,12 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På samma låga som ullticka. På nytt hygge 2025. Fruktkroppar ännu små.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130137961</v>
+        <v>130135979</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>92056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,34 +2060,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långslotten, Långslotten, Dlr</t>
+          <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540219</v>
+        <v>540153</v>
       </c>
       <c r="R14" t="n">
-        <v>6704341</v>
+        <v>6704402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På samma låga som ullticka. På nytt hygge 2025. Fruktkroppar ännu små.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2173,7 @@
         <v>130136085</v>
       </c>
       <c r="B15" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130136105</v>
       </c>
       <c r="B16" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130135908</v>
       </c>
       <c r="B17" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>130135988</v>
       </c>
       <c r="B18" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>130136026</v>
       </c>
       <c r="B19" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 16482-2025 artfynd.xlsx
+++ b/artfynd/A 16482-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130137046</v>
       </c>
       <c r="B3" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130137508</v>
+        <v>130137042</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>92212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,48 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540250</v>
+        <v>540241</v>
       </c>
       <c r="R4" t="n">
-        <v>6704316</v>
+        <v>6704273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På liten yta.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130137042</v>
+        <v>130137508</v>
       </c>
       <c r="B5" t="n">
-        <v>92211</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +1017,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540241</v>
+        <v>540250</v>
       </c>
       <c r="R5" t="n">
-        <v>6704273</v>
+        <v>6704316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På liten yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1135,7 @@
         <v>130136051</v>
       </c>
       <c r="B6" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>130135971</v>
       </c>
       <c r="B7" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>130136068</v>
       </c>
       <c r="B8" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>130138039</v>
       </c>
       <c r="B9" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>130136490</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>130138048</v>
       </c>
       <c r="B11" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130137961</v>
+        <v>130137037</v>
       </c>
       <c r="B12" t="n">
-        <v>91758</v>
+        <v>92057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,34 +1837,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540219</v>
+        <v>540244</v>
       </c>
       <c r="R12" t="n">
-        <v>6704341</v>
+        <v>6704273</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130137037</v>
+        <v>130135979</v>
       </c>
       <c r="B13" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1972,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1973,14 +1982,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långslotten, Långslotten, Dlr</t>
+          <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540244</v>
+        <v>540153</v>
       </c>
       <c r="R13" t="n">
-        <v>6704273</v>
+        <v>6704402</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2031,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På samma låga som ullticka. På nytt hygge 2025. Fruktkroppar ännu små.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130135979</v>
+        <v>130137961</v>
       </c>
       <c r="B14" t="n">
-        <v>92056</v>
+        <v>91759</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,43 +2074,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
+          <t>Långslotten, Långslotten, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540153</v>
+        <v>540219</v>
       </c>
       <c r="R14" t="n">
-        <v>6704402</v>
+        <v>6704341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På samma låga som ullticka. På nytt hygge 2025. Fruktkroppar ännu små.</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2173,7 @@
         <v>130136085</v>
       </c>
       <c r="B15" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>130136105</v>
       </c>
       <c r="B16" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>130135908</v>
       </c>
       <c r="B17" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130135988</v>
+        <v>130136026</v>
       </c>
       <c r="B18" t="n">
-        <v>92056</v>
+        <v>91759</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,43 +2535,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540151</v>
+        <v>540175</v>
       </c>
       <c r="R18" t="n">
-        <v>6704400</v>
+        <v>6704392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,10 +2631,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130136026</v>
+        <v>130135988</v>
       </c>
       <c r="B19" t="n">
-        <v>91758</v>
+        <v>92057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,34 +2642,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ramsnäsholm, Ramsnäsholm, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540175</v>
+        <v>540151</v>
       </c>
       <c r="R19" t="n">
-        <v>6704392</v>
+        <v>6704400</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
